--- a/metadata/table_column_names.xlsx
+++ b/metadata/table_column_names.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mr_gwas_overlap" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mr_magma" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mr_eqtlgen" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scdrs_pathway" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scdeepid_b_cells_sle" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mr_summary" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ti_drug_mr" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crohns_immune" sheetId="13" state="visible" r:id="rId13"/>
